--- a/SINGLE-MATRIX.xlsx
+++ b/SINGLE-MATRIX.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lbdev/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C861CE97-A470-1349-9DF4-251B7F4125CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307611A5-403D-984E-9136-BF01A355E709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="21680" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="21680" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="READ-ME-FIRST" sheetId="10" r:id="rId1"/>
@@ -718,7 +718,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="276">
   <si>
     <t>Positions, Income Statament and &amp; Balance Sheet</t>
   </si>
@@ -1547,13 +1547,16 @@
     <t xml:space="preserve">   ΔC+   </t>
   </si>
   <si>
-    <t>NOT BEING USED TO GENERRATE REPORTS</t>
-  </si>
-  <si>
     <t xml:space="preserve">A Sole Proprietor’s Double-Entry </t>
   </si>
   <si>
     <t xml:space="preserve">A Sole Proprietor’s Closed Single-Entry </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INCLUDED TO ILLUSTRATE THE CONVENTIONAL ACCOUNTING JOURNAL  REPRESENTATION; NOT USED </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INCLUDED TO ILLUSTRATE THE CONVENTIONAL ACCOUNTING LEDGER REPRESENTATION; NOT USED </t>
   </si>
 </sst>
 </file>
@@ -2329,6 +2332,8 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="23" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2343,9 +2348,7 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="23" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3465,7 +3468,7 @@
   <sheetData>
     <row r="2" spans="2:85" ht="47" x14ac:dyDescent="0.55000000000000004">
       <c r="C2" s="111" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="2:85" ht="47" x14ac:dyDescent="0.55000000000000004">
@@ -3563,12 +3566,12 @@
     </row>
     <row r="9" spans="2:85" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="6"/>
-      <c r="C9" s="154" t="s">
+      <c r="C9" s="148" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="27"/>
-      <c r="F9" s="153" t="s">
+      <c r="F9" s="147" t="s">
         <v>10</v>
       </c>
       <c r="G9" s="26"/>
@@ -3902,7 +3905,7 @@
       <c r="R21" s="5"/>
     </row>
     <row r="22" spans="2:23" ht="21.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="147" t="s">
+      <c r="B22" s="149" t="s">
         <v>207</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -3928,7 +3931,7 @@
       <c r="R22" s="1"/>
     </row>
     <row r="23" spans="2:23" ht="22.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="148"/>
+      <c r="B23" s="150"/>
       <c r="C23" s="12"/>
       <c r="D23" s="84"/>
       <c r="E23" s="84"/>
@@ -4976,7 +4979,7 @@
   <sheetData>
     <row r="2" spans="2:92" ht="63" x14ac:dyDescent="0.75">
       <c r="C2" s="112" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="2:92" ht="63" x14ac:dyDescent="0.75">
@@ -5086,12 +5089,12 @@
     </row>
     <row r="9" spans="2:92" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="6"/>
-      <c r="C9" s="154" t="s">
+      <c r="C9" s="148" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="26"/>
       <c r="E9" s="27"/>
-      <c r="F9" s="153" t="s">
+      <c r="F9" s="147" t="s">
         <v>10</v>
       </c>
       <c r="G9" s="26"/>
@@ -5463,26 +5466,26 @@
       <c r="C21" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="149" t="s">
+      <c r="D21" s="151" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="150"/>
-      <c r="F21" s="149" t="s">
+      <c r="E21" s="152"/>
+      <c r="F21" s="151" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="150"/>
-      <c r="H21" s="149" t="s">
+      <c r="G21" s="152"/>
+      <c r="H21" s="151" t="s">
         <v>23</v>
       </c>
-      <c r="I21" s="150"/>
-      <c r="J21" s="149" t="s">
+      <c r="I21" s="152"/>
+      <c r="J21" s="151" t="s">
         <v>24</v>
       </c>
-      <c r="K21" s="150"/>
-      <c r="L21" s="149" t="s">
+      <c r="K21" s="152"/>
+      <c r="L21" s="151" t="s">
         <v>215</v>
       </c>
-      <c r="M21" s="150"/>
+      <c r="M21" s="152"/>
       <c r="N21" s="70"/>
       <c r="O21" s="71"/>
       <c r="P21" s="71"/>
@@ -5490,7 +5493,7 @@
       <c r="Y21" s="5"/>
     </row>
     <row r="22" spans="2:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="151" t="s">
+      <c r="B22" s="153" t="s">
         <v>207</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -5532,7 +5535,7 @@
       <c r="Q22" s="74"/>
     </row>
     <row r="23" spans="2:25" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="151"/>
+      <c r="B23" s="153"/>
       <c r="C23" s="8"/>
       <c r="D23" s="91" t="s">
         <v>196</v>
@@ -5570,7 +5573,7 @@
       <c r="Q23" s="74"/>
     </row>
     <row r="24" spans="2:25" ht="21.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="152"/>
+      <c r="B24" s="154"/>
       <c r="C24" s="8" t="s">
         <v>28</v>
       </c>
@@ -5611,7 +5614,7 @@
       <c r="Y24" s="1"/>
     </row>
     <row r="25" spans="2:25" ht="22.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="152"/>
+      <c r="B25" s="154"/>
       <c r="C25" s="12" t="s">
         <v>36</v>
       </c>
@@ -7081,9 +7084,9 @@
         <v>219</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:7" ht="19" x14ac:dyDescent="0.25">
       <c r="B6" s="155" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="17" customHeight="1" x14ac:dyDescent="0.25">
@@ -8870,9 +8873,9 @@
         <v>216</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:6" ht="17" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="155" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="53" customHeight="1" x14ac:dyDescent="0.3">
